--- a/outputs/379-36.xlsx
+++ b/outputs/379-36.xlsx
@@ -169,24 +169,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -411,304 +415,304 @@
   <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="35.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="35.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="4" t="n">
         <v>44459</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>-2472.13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="4" t="n">
         <v>44457</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>-270.28</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>44454</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>-50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>44456</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>1037.6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3" t="n">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>44447</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>833</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>44442</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>1151.09</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>44454</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>1126.47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>44452</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>1011.1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="3" t="n">
+      <c r="A10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>44454</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>-816</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="0" t="s">
+      <c r="A11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="4" t="n">
         <v>44459</v>
       </c>
-      <c r="E11" s="0" t="s">
+      <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>-7999.29</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="A12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>44452</v>
       </c>
-      <c r="E12" s="0" t="s">
+      <c r="E12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <v>41.09</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="A13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>44453</v>
       </c>
-      <c r="E13" s="0" t="s">
+      <c r="E13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>-2169.05</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="3" t="n">
+      <c r="A14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="4" t="n">
         <v>44447</v>
       </c>
-      <c r="E14" s="0" t="s">
+      <c r="E14" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>146.31</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="0" t="s">
+      <c r="A15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="4" t="n">
         <v>44457</v>
       </c>
-      <c r="E15" s="0" t="s">
+      <c r="E15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>-2145.72</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="3" t="n">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="4" t="n">
         <v>44454</v>
       </c>
-      <c r="E16" s="0" t="s">
+      <c r="E16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>-9990.35</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="3" t="n">
+      <c r="A17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4" t="n">
         <v>44441</v>
       </c>
-      <c r="E17" s="0" t="s">
+      <c r="E17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>-128.29</v>
       </c>
     </row>

--- a/outputs/379-36.xlsx
+++ b/outputs/379-36.xlsx
@@ -596,6 +596,7 @@
       <c r="F10" s="5" t="n">
         <v>-816</v>
       </c>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
@@ -613,6 +614,7 @@
       <c r="F11" s="5" t="n">
         <v>-7999.29</v>
       </c>
+      <c r="H11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
